--- a/questionnaire_templates/004_cultural_diversity_and_immigration_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/004_cultural_diversity_and_immigration_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'elementary_school'}</t>
+          <t>elementary_school</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Elementary School'}</t>
+          <t>Elementary School</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'university'}</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'University'}</t>
+          <t>University</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'$0-20,000'}</t>
+          <t>$0-20,000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '$0-20,000'}</t>
+          <t>$0-20,000</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'$20,001-50,000'}</t>
+          <t>$20,001-50,000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '$20,001-50,000'}</t>
+          <t>$20,001-50,000</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'$50,001-100,000'}</t>
+          <t>$50,001-100,000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '$50,001-100,000'}</t>
+          <t>$50,001-100,000</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'$100,001_or_more'}</t>
+          <t>$100,001_or_more</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '$100,001 or more'}</t>
+          <t>$100,001 or more</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'divorced'}</t>
+          <t>divorced</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Divorced'}</t>
+          <t>Divorced</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'widowed'}</t>
+          <t>widowed</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Widowed'}</t>
+          <t>Widowed</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1-2'}</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1-2'}</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'3-5'}</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '3-5'}</t>
+          <t>3-5</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'11_or_more'}</t>
+          <t>11_or_more</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '11 or more'}</t>
+          <t>11 or more</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'asian'}</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Asian'}</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'black_or_african_american'}</t>
+          <t>black_or_african_american</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Black or African American'}</t>
+          <t>Black or African American</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hispanic_or_latino'}</t>
+          <t>hispanic_or_latino</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hispanic or Latino'}</t>
+          <t>Hispanic or Latino</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'american_indian_or_alaska_native'}</t>
+          <t>american_indian_or_alaska_native</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'American Indian or Alaska Native'}</t>
+          <t>American Indian or Alaska Native</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'asian'}</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Asian'}</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'black_or_african_american'}</t>
+          <t>black_or_african_american</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Black or African American'}</t>
+          <t>Black or African American</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'native_hawaiian_or_other_pacific_islander'}</t>
+          <t>native_hawaiian_or_other_pacific_islander</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Native Hawaiian or Other Pacific Islander'}</t>
+          <t>Native Hawaiian or Other Pacific Islander</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'some_other_race_or_ethnicity'}</t>
+          <t>some_other_race_or_ethnicity</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Some other race or ethnicity'}</t>
+          <t>Some other race or ethnicity</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'0-17'}</t>
+          <t>0-17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '0-17'}</t>
+          <t>0-17</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'18-24'}</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '18-24'}</t>
+          <t>18-24</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'55-64'}</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': '55-64'}</t>
+          <t>55-64</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'65_or_older'}</t>
+          <t>65_or_older</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': '65 or older'}</t>
+          <t>65 or older</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'elementary_school'}</t>
+          <t>elementary_school</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Elementary School'}</t>
+          <t>Elementary School</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Some college'}</t>
+          <t>Some college</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'some_other'}</t>
+          <t>some_other</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Some other'}</t>
+          <t>Some other</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'$0-20,000'}</t>
+          <t>$0-20,000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '$0-20,000'}</t>
+          <t>$0-20,000</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'$20,001-50,000'}</t>
+          <t>$20,001-50,000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '$20,001-50,000'}</t>
+          <t>$20,001-50,000</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'$50,001-100,000'}</t>
+          <t>$50,001-100,000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '$50,001-100,000'}</t>
+          <t>$50,001-100,000</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'$100,001_or_more'}</t>
+          <t>$100,001_or_more</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '$100,001 or more'}</t>
+          <t>$100,001 or more</t>
         </is>
       </c>
     </row>
